--- a/data/trans_camb/IP1020-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,27</t>
+          <t>-1,07; 4,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,0</t>
+          <t>-3,7; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,22</t>
+          <t>-0,31; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,32</t>
+          <t>0,41; 4,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,33</t>
+          <t>0,44; 4,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,92</t>
+          <t>0,25; 2,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,14</t>
+          <t>0,14; 3,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,67</t>
+          <t>-0,66; 1,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,76</t>
+          <t>0,21; 3,73</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,82; —</t>
+          <t>-53,25; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-33,99; —</t>
+          <t>-61,23; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,88</t>
+          <t>-1,02; 3,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,71</t>
+          <t>-1,66; 2,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,82</t>
+          <t>-1,0; 3,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,07</t>
+          <t>-3,75; -0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,21</t>
+          <t>-3,08; 1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,79</t>
+          <t>0,17; 5,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,27</t>
+          <t>-1,67; 1,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,41</t>
+          <t>-1,53; 1,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,02</t>
+          <t>0,31; 3,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 673,21</t>
+          <t>-51,03; 639,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 397,65</t>
+          <t>-67,14; 372,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 557,08</t>
+          <t>-54,11; 578,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,82</t>
+          <t>-100,0; 30,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 154,04</t>
+          <t>-86,74; 102,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 476,19</t>
+          <t>-10,43; 461,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,28; 120,19</t>
+          <t>-65,35; 96,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 144,31</t>
+          <t>-59,32; 123,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 336,12</t>
+          <t>7,39; 307,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,74</t>
+          <t>0,95; 5,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,81</t>
+          <t>0,66; 3,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,88</t>
+          <t>2,18; 7,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,65</t>
+          <t>-0,65; 1,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,3</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,81</t>
+          <t>0,59; 4,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,73</t>
+          <t>0,48; 2,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,91</t>
+          <t>0,57; 2,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,33</t>
+          <t>1,78; 5,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,12</t>
+          <t>0,4; 4,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,26</t>
+          <t>-0,42; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,08</t>
+          <t>0,7; 5,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,39</t>
+          <t>0,31; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,68</t>
+          <t>-0,09; 3,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,8</t>
+          <t>0,95; 6,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,74</t>
+          <t>0,91; 3,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,41</t>
+          <t>0,05; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,56</t>
+          <t>1,12; 4,63</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,79; —</t>
+          <t>-37,08; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-49,63; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; —</t>
+          <t>-15,47; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,96; 2034,92</t>
+          <t>53,78; 2069,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 1261,6</t>
+          <t>-21,93; 1611,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,61; 2264,52</t>
+          <t>59,23; 2641,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,04</t>
+          <t>0,75; 2,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,47</t>
+          <t>-0,37; 1,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,18</t>
+          <t>1,36; 4,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,38</t>
+          <t>-0,41; 1,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,9</t>
+          <t>-0,2; 1,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,64</t>
+          <t>1,19; 3,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,85</t>
+          <t>0,4; 1,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,35</t>
+          <t>0,05; 1,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,38</t>
+          <t>1,56; 3,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>48,72; 745,99</t>
+          <t>53,35; 727,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 324,19</t>
+          <t>-38,64; 275,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90,64; 920,37</t>
+          <t>91,19; 1030,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 260,01</t>
+          <t>-37,85; 282,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 346,06</t>
+          <t>-19,9; 353,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,48; 714,68</t>
+          <t>73,47; 683,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,91; 316,97</t>
+          <t>28,46; 305,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 251,82</t>
+          <t>0,32; 236,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>149,64; 594,62</t>
+          <t>126,24; 593,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Habitat-trans_camb.xlsx
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,02</t>
+          <t>-1,08; 4,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,0</t>
+          <t>-3,65; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,03</t>
+          <t>-0,48; 6,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,53</t>
+          <t>0,43; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,98</t>
+          <t>0,26; 2,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,31</t>
+          <t>0,06; 3,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,71</t>
+          <t>-0,75; 1,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,73</t>
+          <t>0,25; 4,05</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,25; —</t>
+          <t>-57,97; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,23; —</t>
+          <t>-55,29; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,6</t>
+          <t>-0,93; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,47</t>
+          <t>-1,75; 2,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,87</t>
+          <t>-0,96; 3,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,0</t>
+          <t>-3,71; 0,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,05</t>
+          <t>-3,16; 1,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 5,68</t>
+          <t>0,11; 5,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,12</t>
+          <t>-1,77; 1,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,36</t>
+          <t>-1,65; 1,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,89</t>
+          <t>0,3; 4,22</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,03; 639,84</t>
+          <t>-45,0; 658,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,14; 372,75</t>
+          <t>-70,19; 445,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 578,37</t>
+          <t>-51,39; 708,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,53</t>
+          <t>-100,0; 76,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,74; 102,61</t>
+          <t>-85,8; 148,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 461,15</t>
+          <t>-8,04; 521,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 96,45</t>
+          <t>-64,66; 116,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 123,87</t>
+          <t>-61,48; 120,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 307,66</t>
+          <t>-2,35; 340,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,02</t>
+          <t>0,91; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,79</t>
+          <t>0,68; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,88</t>
+          <t>2,11; 7,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,83</t>
+          <t>-0,64; 1,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,02; 3,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,61</t>
+          <t>0,6; 4,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,88</t>
+          <t>0,46; 2,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,83</t>
+          <t>0,52; 2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,02</t>
+          <t>1,77; 5,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,71</t>
+          <t>0,61; 5,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,52</t>
+          <t>-0,4; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,04</t>
+          <t>0,61; 4,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,49</t>
+          <t>0,37; 4,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,83</t>
+          <t>-0,02; 3,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,15</t>
+          <t>0,91; 6,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,88</t>
+          <t>0,87; 3,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,42</t>
+          <t>-0,02; 2,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,63</t>
+          <t>1,22; 4,68</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,08; —</t>
+          <t>-43,33; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,63; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,47; —</t>
+          <t>4,58; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,78; 2069,38</t>
+          <t>39,33; 2076,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 1611,69</t>
+          <t>-40,26; 1420,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,23; 2641,61</t>
+          <t>42,98; 2183,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,97</t>
+          <t>0,63; 2,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,38</t>
+          <t>-0,4; 1,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,11</t>
+          <t>1,24; 3,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,47</t>
+          <t>-0,33; 1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,73</t>
+          <t>-0,0; 1,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,78</t>
+          <t>1,24; 3,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,49; 2,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,38</t>
+          <t>0,04; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,39</t>
+          <t>1,56; 3,44</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>53,35; 727,08</t>
+          <t>36,56; 625,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 275,26</t>
+          <t>-41,22; 344,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91,19; 1030,84</t>
+          <t>92,72; 916,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 282,23</t>
+          <t>-30,0; 276,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 353,11</t>
+          <t>-6,08; 342,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,47; 683,91</t>
+          <t>86,73; 683,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,46; 305,26</t>
+          <t>38,29; 339,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,32; 236,6</t>
+          <t>0,36; 230,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,24; 593,56</t>
+          <t>129,02; 596,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,05</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,44</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,33</t>
+          <t>0,41; 4,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,0</t>
+          <t>0,43; 4,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 6,98</t>
+          <t>0,2; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,41</t>
+          <t>-1,09; 4,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,21</t>
+          <t>-3,68; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,91</t>
+          <t>-0,11; 7,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,18</t>
+          <t>0,05; 3,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,61</t>
+          <t>-0,75; 1,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,05</t>
+          <t>0,27; 4,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>114,85%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>233,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>245,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>335,44%</t>
+          <t>364,72%</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,97; —</t>
+          <t>-48,82; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,29; —</t>
+          <t>-32,11; —</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,47</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>2,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,77</t>
+          <t>-3,68; 0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,53</t>
+          <t>-2,86; 1,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,63</t>
+          <t>-0,03; 6,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,28</t>
+          <t>-0,69; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,15</t>
+          <t>-1,41; 2,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 5,84</t>
+          <t>-0,81; 4,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,27</t>
+          <t>-1,73; 1,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,31</t>
+          <t>-1,65; 1,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,22</t>
+          <t>0,21; 4,14</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-70,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-31,67%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>127,22%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>77,75%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>29,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-70,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-31,67%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>123,11%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108,14%</t>
+          <t>111,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 658,46</t>
+          <t>-100,0; 123,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 445,09</t>
+          <t>-84,34; 154,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 708,45</t>
+          <t>-13,61; 498,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,59</t>
+          <t>-42,11; 673,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,8; 148,23</t>
+          <t>-67,93; 397,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 521,79</t>
+          <t>-47,53; 581,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 116,76</t>
+          <t>-63,28; 120,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 120,61</t>
+          <t>-60,88; 144,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 340,98</t>
+          <t>1,75; 333,08</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,73</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>3,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,88</t>
+          <t>-0,64; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,96</t>
+          <t>-0,19; 3,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,95</t>
+          <t>0,74; 5,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,9</t>
+          <t>0,8; 4,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,46</t>
+          <t>0,59; 3,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,85</t>
+          <t>2,92; 9,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,79</t>
+          <t>0,4; 2,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,84</t>
+          <t>0,61; 2,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,28</t>
+          <t>2,38; 6,3</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107,59%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>385,07%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>735,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>107,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>385,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>632,63%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>787,29%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1919,21%</t>
+          <t>2338,53%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,08</t>
+          <t>0,39; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,51</t>
+          <t>-0,06; 3,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,9</t>
+          <t>0,78; 6,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,37</t>
+          <t>0,68; 5,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,99</t>
+          <t>-0,41; 2,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,13</t>
+          <t>0,72; 5,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,78</t>
+          <t>0,86; 3,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,38</t>
+          <t>-0,04; 2,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,68</t>
+          <t>1,27; 4,69</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>318,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>238,16%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>473,57%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>620,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>191,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>634,27%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>318,9%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>238,16%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>455,34%</t>
+          <t>652,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>524,67%</t>
+          <t>540,46%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,79; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,9; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,33; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,58; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,33; 2076,18</t>
+          <t>48,96; 2034,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 1420,37</t>
+          <t>-36,18; 1261,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,98; 2183,28</t>
+          <t>92,59; 2374,38</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,92</t>
+          <t>-0,46; 1,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,38</t>
+          <t>-0,01; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,96</t>
+          <t>1,3; 3,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,51</t>
+          <t>0,76; 3,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 1,85</t>
+          <t>-0,29; 1,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,7</t>
+          <t>1,59; 4,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,0</t>
+          <t>0,51; 1,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,36</t>
+          <t>0,04; 1,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,44</t>
+          <t>1,69; 3,69</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>56,77%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>281,7%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>226,84%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>66,41%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>324,27%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>264,08%</t>
+          <t>364,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>291,23%</t>
+          <t>318,77%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>36,56; 625,38</t>
+          <t>-38,49; 260,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 344,38</t>
+          <t>-9,53; 346,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92,72; 916,96</t>
+          <t>90,5; 749,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 276,77</t>
+          <t>48,72; 745,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 342,84</t>
+          <t>-28,3; 324,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,73; 683,46</t>
+          <t>109,52; 1001,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,29; 339,17</t>
+          <t>37,91; 316,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,36; 230,18</t>
+          <t>-3,66; 251,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>129,02; 596,11</t>
+          <t>159,21; 638,68</t>
         </is>
       </c>
     </row>
